--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/155.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/155.xlsx
@@ -426,13 +426,13 @@
         <v>-13.81562856161115</v>
       </c>
       <c r="E2">
-        <v>-16.53299424588929</v>
+        <v>-16.07717163769921</v>
       </c>
       <c r="F2">
-        <v>-0.1200015910540581</v>
+        <v>-0.9173458062513195</v>
       </c>
       <c r="G2">
-        <v>-8.976631454586178</v>
+        <v>-8.021102074495257</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.0484485262915</v>
       </c>
       <c r="E3">
-        <v>-16.51337689648806</v>
+        <v>-17.13394991755119</v>
       </c>
       <c r="F3">
-        <v>-0.428167518773919</v>
+        <v>-0.85217151573386</v>
       </c>
       <c r="G3">
-        <v>-8.873256359576896</v>
+        <v>-7.676305446034624</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.28211664783514</v>
       </c>
       <c r="E4">
-        <v>-17.27894259832878</v>
+        <v>-16.63051040517046</v>
       </c>
       <c r="F4">
-        <v>-0.05679550148565025</v>
+        <v>-0.7694532319925097</v>
       </c>
       <c r="G4">
-        <v>-8.302121043141831</v>
+        <v>-7.975674768605378</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.61569653585316</v>
       </c>
       <c r="E5">
-        <v>-18.14179350727628</v>
+        <v>-18.61842898200561</v>
       </c>
       <c r="F5">
-        <v>-0.2571875166316843</v>
+        <v>-0.704292195353495</v>
       </c>
       <c r="G5">
-        <v>-7.512446684022858</v>
+        <v>-7.600798523374927</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.04857375885526</v>
       </c>
       <c r="E6">
-        <v>-18.63720403524141</v>
+        <v>-18.7677916402006</v>
       </c>
       <c r="F6">
-        <v>-0.3690535641753407</v>
+        <v>-0.7591069231315439</v>
       </c>
       <c r="G6">
-        <v>-7.375496036154287</v>
+        <v>-7.298155071265834</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.60420145289991</v>
       </c>
       <c r="E7">
-        <v>-18.46896216890844</v>
+        <v>-18.60482091761256</v>
       </c>
       <c r="F7">
-        <v>-0.3178380927624557</v>
+        <v>-0.4955982820966044</v>
       </c>
       <c r="G7">
-        <v>-7.187208758608238</v>
+        <v>-6.861527220091356</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.28661848732915</v>
       </c>
       <c r="E8">
-        <v>-18.36558616426134</v>
+        <v>-19.7755808882376</v>
       </c>
       <c r="F8">
-        <v>-0.1149601470406203</v>
+        <v>-0.2547479746304397</v>
       </c>
       <c r="G8">
-        <v>-6.492573540830661</v>
+        <v>-7.15131251332592</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.09321310215338</v>
       </c>
       <c r="E9">
-        <v>-20.37798567158196</v>
+        <v>-19.75734472340871</v>
       </c>
       <c r="F9">
-        <v>-0.07614285054543551</v>
+        <v>-0.3976297544697152</v>
       </c>
       <c r="G9">
-        <v>-6.120107372752799</v>
+        <v>-6.610438893665333</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.00652690483861</v>
       </c>
       <c r="E10">
-        <v>-19.93448051269274</v>
+        <v>-21.70740525753974</v>
       </c>
       <c r="F10">
-        <v>0.3678736744987387</v>
+        <v>-0.2380679686076689</v>
       </c>
       <c r="G10">
-        <v>-6.124040300853453</v>
+        <v>-6.024882840861203</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.0167519052953</v>
       </c>
       <c r="E11">
-        <v>-20.71791557296773</v>
+        <v>-20.82538078964376</v>
       </c>
       <c r="F11">
-        <v>0.5410836416893097</v>
+        <v>-0.02228737221982845</v>
       </c>
       <c r="G11">
-        <v>-6.27835807062104</v>
+        <v>-6.390171746209925</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.09801864373841</v>
       </c>
       <c r="E12">
-        <v>-20.92666916777332</v>
+        <v>-22.84503491232466</v>
       </c>
       <c r="F12">
-        <v>0.3506320353768698</v>
+        <v>0.03305254049159532</v>
       </c>
       <c r="G12">
-        <v>-5.678927521461825</v>
+        <v>-6.20818112627957</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.22552689726924</v>
       </c>
       <c r="E13">
-        <v>-22.98526363844618</v>
+        <v>-21.94124659834782</v>
       </c>
       <c r="F13">
-        <v>0.5950434943076696</v>
+        <v>0.3874289437766266</v>
       </c>
       <c r="G13">
-        <v>-5.582517814267169</v>
+        <v>-5.642451930710134</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.38505128720507</v>
       </c>
       <c r="E14">
-        <v>-24.0601331719588</v>
+        <v>-23.62784504318659</v>
       </c>
       <c r="F14">
-        <v>0.6803520829175738</v>
+        <v>0.8876162340372326</v>
       </c>
       <c r="G14">
-        <v>-5.379094722515572</v>
+        <v>-5.944555763896327</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.55265621086633</v>
       </c>
       <c r="E15">
-        <v>-23.99307552885322</v>
+        <v>-23.05271525879043</v>
       </c>
       <c r="F15">
-        <v>0.6133578692161638</v>
+        <v>0.7674400047086914</v>
       </c>
       <c r="G15">
-        <v>-5.311662220426157</v>
+        <v>-5.633914033764354</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.7090738807306</v>
       </c>
       <c r="E16">
-        <v>-23.82894098844521</v>
+        <v>-24.98618799263136</v>
       </c>
       <c r="F16">
-        <v>1.462541316480618</v>
+        <v>1.120727104859041</v>
       </c>
       <c r="G16">
-        <v>-5.186205786669936</v>
+        <v>-5.201023788503715</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.84652024911674</v>
       </c>
       <c r="E17">
-        <v>-26.25037038203464</v>
+        <v>-24.9208556981227</v>
       </c>
       <c r="F17">
-        <v>0.5005532814051356</v>
+        <v>1.506487863933938</v>
       </c>
       <c r="G17">
-        <v>-4.428488123641547</v>
+        <v>-5.044236351763831</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.95083874065863</v>
       </c>
       <c r="E18">
-        <v>-26.53359473189636</v>
+        <v>-26.77347252855667</v>
       </c>
       <c r="F18">
-        <v>1.749471217462311</v>
+        <v>1.513323551741839</v>
       </c>
       <c r="G18">
-        <v>-4.028355726491996</v>
+        <v>-4.864629324621752</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.01542583709081</v>
       </c>
       <c r="E19">
-        <v>-25.59976904982665</v>
+        <v>-26.95597908801381</v>
       </c>
       <c r="F19">
-        <v>1.903144967825258</v>
+        <v>2.049635116071129</v>
       </c>
       <c r="G19">
-        <v>-4.571354716388796</v>
+        <v>-4.25986548659877</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.0445179501237</v>
       </c>
       <c r="E20">
-        <v>-28.59427682908676</v>
+        <v>-28.14104450802908</v>
       </c>
       <c r="F20">
-        <v>1.961823201169964</v>
+        <v>2.497024753179502</v>
       </c>
       <c r="G20">
-        <v>-4.205178584835549</v>
+        <v>-3.942705292299972</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-11.03620175635692</v>
       </c>
       <c r="E21">
-        <v>-27.26480290144089</v>
+        <v>-28.86797779811036</v>
       </c>
       <c r="F21">
-        <v>2.588226347492922</v>
+        <v>2.453727645769978</v>
       </c>
       <c r="G21">
-        <v>-4.224157942412191</v>
+        <v>-4.378922635827579</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.99476928798609</v>
       </c>
       <c r="E22">
-        <v>-27.08472360405187</v>
+        <v>-28.38480320691395</v>
       </c>
       <c r="F22">
-        <v>2.607426247155009</v>
+        <v>2.438901525994672</v>
       </c>
       <c r="G22">
-        <v>-3.432914384707602</v>
+        <v>-3.980971888188408</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.93140583713649</v>
       </c>
       <c r="E23">
-        <v>-29.16030890920151</v>
+        <v>-29.87419340142969</v>
       </c>
       <c r="F23">
-        <v>2.383821720647727</v>
+        <v>2.482233424835115</v>
       </c>
       <c r="G23">
-        <v>-4.211855955188259</v>
+        <v>-3.851738121971878</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.84803475225762</v>
       </c>
       <c r="E24">
-        <v>-29.83295485287884</v>
+        <v>-29.74440960060686</v>
       </c>
       <c r="F24">
-        <v>2.704573862685724</v>
+        <v>2.754902152610211</v>
       </c>
       <c r="G24">
-        <v>-3.107888334207496</v>
+        <v>-3.285499102389395</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.7512230315479</v>
       </c>
       <c r="E25">
-        <v>-30.73466233304916</v>
+        <v>-30.4419712082744</v>
       </c>
       <c r="F25">
-        <v>2.550616810671019</v>
+        <v>2.972114996237492</v>
       </c>
       <c r="G25">
-        <v>-2.654214484051312</v>
+        <v>-3.916780410181939</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.65306102429794</v>
       </c>
       <c r="E26">
-        <v>-30.65629029763542</v>
+        <v>-30.88115620296029</v>
       </c>
       <c r="F26">
-        <v>2.500734182409238</v>
+        <v>2.763243812356402</v>
       </c>
       <c r="G26">
-        <v>-1.959172069172405</v>
+        <v>-3.361049062141103</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.55530729871813</v>
       </c>
       <c r="E27">
-        <v>-29.29757601332201</v>
+        <v>-30.18133262252593</v>
       </c>
       <c r="F27">
-        <v>2.553371960652731</v>
+        <v>2.881899159133403</v>
       </c>
       <c r="G27">
-        <v>-3.14270865218955</v>
+        <v>-3.159731477352483</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.46434162948775</v>
       </c>
       <c r="E28">
-        <v>-31.56747813814079</v>
+        <v>-30.74475630161226</v>
       </c>
       <c r="F28">
-        <v>2.874064460237725</v>
+        <v>2.113714304882087</v>
       </c>
       <c r="G28">
-        <v>-3.721938252468134</v>
+        <v>-3.45767726534135</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.39206355540472</v>
       </c>
       <c r="E29">
-        <v>-30.6356766839525</v>
+        <v>-30.58659255418336</v>
       </c>
       <c r="F29">
-        <v>1.972560499445051</v>
+        <v>2.547932900285949</v>
       </c>
       <c r="G29">
-        <v>-2.96796481644466</v>
+        <v>-3.191582235985811</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.33916519061385</v>
       </c>
       <c r="E30">
-        <v>-30.82881157190563</v>
+        <v>-30.28661511473026</v>
       </c>
       <c r="F30">
-        <v>2.394066968685552</v>
+        <v>2.403773777911556</v>
       </c>
       <c r="G30">
-        <v>-3.397292914705044</v>
+        <v>-4.078609807778133</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.31043374351275</v>
       </c>
       <c r="E31">
-        <v>-28.86855291430933</v>
+        <v>-29.42574767739811</v>
       </c>
       <c r="F31">
-        <v>2.176207998484088</v>
+        <v>2.143865221609183</v>
       </c>
       <c r="G31">
-        <v>-2.884231188119874</v>
+        <v>-3.666357503409309</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.31394578752567</v>
       </c>
       <c r="E32">
-        <v>-29.40920289761109</v>
+        <v>-30.48815711467863</v>
       </c>
       <c r="F32">
-        <v>2.218517691949475</v>
+        <v>2.203042132130375</v>
       </c>
       <c r="G32">
-        <v>-3.032636323554323</v>
+        <v>-3.235433722198997</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.34476011164175</v>
       </c>
       <c r="E33">
-        <v>-29.34848058964224</v>
+        <v>-29.92283600498308</v>
       </c>
       <c r="F33">
-        <v>1.871575886104569</v>
+        <v>2.065168661608425</v>
       </c>
       <c r="G33">
-        <v>-2.280705494128579</v>
+        <v>-3.042253458345905</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.40222559525286</v>
       </c>
       <c r="E34">
-        <v>-30.65845264397408</v>
+        <v>-29.26906474096972</v>
       </c>
       <c r="F34">
-        <v>1.976965757293139</v>
+        <v>1.965156551598829</v>
       </c>
       <c r="G34">
-        <v>-2.763618082487607</v>
+        <v>-3.266913699731927</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.48728284820867</v>
       </c>
       <c r="E35">
-        <v>-29.6085214168217</v>
+        <v>-29.00833332150409</v>
       </c>
       <c r="F35">
-        <v>2.500228878293531</v>
+        <v>2.1110254242926</v>
       </c>
       <c r="G35">
-        <v>-3.739792024561423</v>
+        <v>-2.717038706750061</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.58785790927984</v>
       </c>
       <c r="E36">
-        <v>-28.49868074278484</v>
+        <v>-29.04072096760695</v>
       </c>
       <c r="F36">
-        <v>2.309136115611324</v>
+        <v>2.236738461341453</v>
       </c>
       <c r="G36">
-        <v>-3.699684765353153</v>
+        <v>-3.381696934669537</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.69687268934054</v>
       </c>
       <c r="E37">
-        <v>-28.18582658749093</v>
+        <v>-28.41276200543731</v>
       </c>
       <c r="F37">
-        <v>2.553106883083835</v>
+        <v>2.190518873734852</v>
       </c>
       <c r="G37">
-        <v>-2.917767014432691</v>
+        <v>-3.839164670013726</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.80955924911687</v>
       </c>
       <c r="E38">
-        <v>-27.0742311297761</v>
+        <v>-27.48384971766592</v>
       </c>
       <c r="F38">
-        <v>2.450750493324316</v>
+        <v>2.604656186560048</v>
       </c>
       <c r="G38">
-        <v>-4.078129778674938</v>
+        <v>-3.110934036103625</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.91143693840454</v>
       </c>
       <c r="E39">
-        <v>-28.27788140711885</v>
+        <v>-27.63606531448574</v>
       </c>
       <c r="F39">
-        <v>1.793285226131182</v>
+        <v>2.302336875969146</v>
       </c>
       <c r="G39">
-        <v>-3.334538213462619</v>
+        <v>-2.890239828273651</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.99481129140885</v>
       </c>
       <c r="E40">
-        <v>-26.45755259635957</v>
+        <v>-26.53303772959342</v>
       </c>
       <c r="F40">
-        <v>2.040880929358343</v>
+        <v>2.531219759567066</v>
       </c>
       <c r="G40">
-        <v>-2.963124798866246</v>
+        <v>-3.357437256957758</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.05497876589095</v>
       </c>
       <c r="E41">
-        <v>-25.89421948675339</v>
+        <v>-26.47222032367041</v>
       </c>
       <c r="F41">
-        <v>1.872458925755954</v>
+        <v>2.32952223739422</v>
       </c>
       <c r="G41">
-        <v>-3.251450141517991</v>
+        <v>-3.850377487755238</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.08011420930701</v>
       </c>
       <c r="E42">
-        <v>-25.73075968897252</v>
+        <v>-25.91416741475718</v>
       </c>
       <c r="F42">
-        <v>1.927724285401125</v>
+        <v>2.49954796028843</v>
       </c>
       <c r="G42">
-        <v>-4.349107862700903</v>
+        <v>-3.304144094866571</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.06589765252611</v>
       </c>
       <c r="E43">
-        <v>-23.47669363775857</v>
+        <v>-25.8917469399452</v>
       </c>
       <c r="F43">
-        <v>2.074732991641148</v>
+        <v>2.566170237025983</v>
       </c>
       <c r="G43">
-        <v>-4.11477751779467</v>
+        <v>-2.568921588777529</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.01117406366093</v>
       </c>
       <c r="E44">
-        <v>-25.44918823212359</v>
+        <v>-25.35394083832026</v>
       </c>
       <c r="F44">
-        <v>2.629727554373178</v>
+        <v>2.439118558254206</v>
       </c>
       <c r="G44">
-        <v>-3.310417578663489</v>
+        <v>-3.526953741296139</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.91128664464803</v>
       </c>
       <c r="E45">
-        <v>-23.94409102551225</v>
+        <v>-23.74305847888974</v>
       </c>
       <c r="F45">
-        <v>2.49952145253154</v>
+        <v>2.83885387541433</v>
       </c>
       <c r="G45">
-        <v>-2.655277169169418</v>
+        <v>-3.071409432910267</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.76769470379825</v>
       </c>
       <c r="E46">
-        <v>-23.34340706229081</v>
+        <v>-24.32368583073121</v>
       </c>
       <c r="F46">
-        <v>2.676205592609452</v>
+        <v>2.555848779187101</v>
       </c>
       <c r="G46">
-        <v>-4.178217501963724</v>
+        <v>-2.5861331150362</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.58581155211745</v>
       </c>
       <c r="E47">
-        <v>-23.41778724786679</v>
+        <v>-24.57074125869367</v>
       </c>
       <c r="F47">
-        <v>2.364305384637771</v>
+        <v>2.461837362643385</v>
       </c>
       <c r="G47">
-        <v>-3.879007085578855</v>
+        <v>-3.496483480152687</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.37020272110665</v>
       </c>
       <c r="E48">
-        <v>-22.62299477478057</v>
+        <v>-23.08152541042723</v>
       </c>
       <c r="F48">
-        <v>2.881329242360277</v>
+        <v>2.323432080248838</v>
       </c>
       <c r="G48">
-        <v>-3.12009100506525</v>
+        <v>-2.879500418544255</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.12814374530012</v>
       </c>
       <c r="E49">
-        <v>-23.15783472593048</v>
+        <v>-23.57677744180209</v>
       </c>
       <c r="F49">
-        <v>2.271501727767337</v>
+        <v>2.573055626878052</v>
       </c>
       <c r="G49">
-        <v>-2.262596810028766</v>
+        <v>-2.401374879035014</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.869323103451192</v>
       </c>
       <c r="E50">
-        <v>-20.35393494612722</v>
+        <v>-22.2664816015787</v>
       </c>
       <c r="F50">
-        <v>2.823230866197531</v>
+        <v>2.771592099041815</v>
       </c>
       <c r="G50">
-        <v>-4.139775447161707</v>
+        <v>-2.872366192907126</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.603183050995103</v>
       </c>
       <c r="E51">
-        <v>-21.15863572034223</v>
+        <v>-22.62654056992857</v>
       </c>
       <c r="F51">
-        <v>2.192833332258274</v>
+        <v>2.106144683555305</v>
       </c>
       <c r="G51">
-        <v>-3.753126901993607</v>
+        <v>-3.460408465411249</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.33771764990594</v>
       </c>
       <c r="E52">
-        <v>-19.98478733044395</v>
+        <v>-22.08256215823118</v>
       </c>
       <c r="F52">
-        <v>2.523870483969429</v>
+        <v>2.529551427617828</v>
       </c>
       <c r="G52">
-        <v>-2.354030767277897</v>
+        <v>-2.601159681238952</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.081774971249493</v>
       </c>
       <c r="E53">
-        <v>-19.71439214744596</v>
+        <v>-20.92543289436923</v>
       </c>
       <c r="F53">
-        <v>2.823043655164498</v>
+        <v>2.815399480771464</v>
       </c>
       <c r="G53">
-        <v>-3.639618227088616</v>
+        <v>-3.662815219682289</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.84551189809077</v>
       </c>
       <c r="E54">
-        <v>-19.78385441024961</v>
+        <v>-21.54487832540445</v>
       </c>
       <c r="F54">
-        <v>2.565794158225112</v>
+        <v>2.587373129068039</v>
       </c>
       <c r="G54">
-        <v>-3.800510740297196</v>
+        <v>-3.594283616473837</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.635080221378836</v>
       </c>
       <c r="E55">
-        <v>-19.60140219248057</v>
+        <v>-21.02217015612108</v>
       </c>
       <c r="F55">
-        <v>2.904806831290421</v>
+        <v>2.747993568470863</v>
       </c>
       <c r="G55">
-        <v>-3.544377142469323</v>
+        <v>-3.238161611723356</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.456688726941307</v>
       </c>
       <c r="E56">
-        <v>-18.2527365919902</v>
+        <v>-20.72526528628218</v>
       </c>
       <c r="F56">
-        <v>2.207256865475819</v>
+        <v>2.68462014868709</v>
       </c>
       <c r="G56">
-        <v>-4.668343769052823</v>
+        <v>-4.440326634489981</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.318177612916497</v>
       </c>
       <c r="E57">
-        <v>-18.82606857220531</v>
+        <v>-20.07094607691389</v>
       </c>
       <c r="F57">
-        <v>2.796173073352488</v>
+        <v>2.870651586538191</v>
       </c>
       <c r="G57">
-        <v>-3.549266818230827</v>
+        <v>-4.182160361700996</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.220429570904884</v>
       </c>
       <c r="E58">
-        <v>-19.21201682645703</v>
+        <v>-20.50038126706127</v>
       </c>
       <c r="F58">
-        <v>2.559533357394753</v>
+        <v>2.60421880857137</v>
       </c>
       <c r="G58">
-        <v>-3.440293590714637</v>
+        <v>-3.624224190331005</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.162497171493959</v>
       </c>
       <c r="E59">
-        <v>-18.97089822791862</v>
+        <v>-19.23219117816121</v>
       </c>
       <c r="F59">
-        <v>2.340587569160816</v>
+        <v>2.975501362180136</v>
       </c>
       <c r="G59">
-        <v>-3.875133747297908</v>
+        <v>-3.933207337147803</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.145819884522576</v>
       </c>
       <c r="E60">
-        <v>-17.71812759301467</v>
+        <v>-19.9028672356452</v>
       </c>
       <c r="F60">
-        <v>2.694237494233592</v>
+        <v>2.853923535206058</v>
       </c>
       <c r="G60">
-        <v>-4.494761934792217</v>
+        <v>-3.522477883727045</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.163929929683425</v>
       </c>
       <c r="E61">
-        <v>-17.18534809753825</v>
+        <v>-18.18672502638039</v>
       </c>
       <c r="F61">
-        <v>2.291384202169331</v>
+        <v>3.147339552951671</v>
       </c>
       <c r="G61">
-        <v>-3.908133265233363</v>
+        <v>-3.946777263313276</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.209907662120616</v>
       </c>
       <c r="E62">
-        <v>-18.05764087479174</v>
+        <v>-18.90512667143122</v>
       </c>
       <c r="F62">
-        <v>2.47826720171051</v>
+        <v>3.015055905663812</v>
       </c>
       <c r="G62">
-        <v>-4.632814994325365</v>
+        <v>-4.097208452617759</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.281956745084184</v>
       </c>
       <c r="E63">
-        <v>-18.49643642071298</v>
+        <v>-18.36103051940963</v>
       </c>
       <c r="F63">
-        <v>2.508969811127871</v>
+        <v>2.686382914520247</v>
       </c>
       <c r="G63">
-        <v>-4.622853562797698</v>
+        <v>-3.720418712065608</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.370480302717617</v>
       </c>
       <c r="E64">
-        <v>-17.84599811356926</v>
+        <v>-17.48559498119481</v>
       </c>
       <c r="F64">
-        <v>3.23344834447268</v>
+        <v>2.850364868843632</v>
       </c>
       <c r="G64">
-        <v>-4.524298622093595</v>
+        <v>-3.901684322522863</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.466617754967418</v>
       </c>
       <c r="E65">
-        <v>-16.85121011440828</v>
+        <v>-18.58192948150378</v>
       </c>
       <c r="F65">
-        <v>2.588832712431771</v>
+        <v>2.878082042141303</v>
       </c>
       <c r="G65">
-        <v>-4.74216893457857</v>
+        <v>-4.771401051690336</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.566944553510481</v>
       </c>
       <c r="E66">
-        <v>-15.65771267579073</v>
+        <v>-19.43323278173173</v>
       </c>
       <c r="F66">
-        <v>2.512921123639225</v>
+        <v>3.057761558747738</v>
       </c>
       <c r="G66">
-        <v>-5.951269550249969</v>
+        <v>-3.962830098633201</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.660432292435985</v>
       </c>
       <c r="E67">
-        <v>-15.61888101117496</v>
+        <v>-18.09929377871429</v>
       </c>
       <c r="F67">
-        <v>2.77195161049463</v>
+        <v>2.775281647453884</v>
       </c>
       <c r="G67">
-        <v>-4.922302338461395</v>
+        <v>-4.572751766606368</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.738123906980126</v>
       </c>
       <c r="E68">
-        <v>-16.23702224169597</v>
+        <v>-18.04351203588781</v>
       </c>
       <c r="F68">
-        <v>2.808285461516222</v>
+        <v>2.570693123045268</v>
       </c>
       <c r="G68">
-        <v>-5.391353672647494</v>
+        <v>-3.561376793813481</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.796999168468435</v>
       </c>
       <c r="E69">
-        <v>-15.06195116381562</v>
+        <v>-18.34443819064552</v>
       </c>
       <c r="F69">
-        <v>2.510974460242646</v>
+        <v>2.302136411057668</v>
       </c>
       <c r="G69">
-        <v>-4.962138132935445</v>
+        <v>-4.724397926123763</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.827320858771262</v>
       </c>
       <c r="E70">
-        <v>-16.74609064726823</v>
+        <v>-18.07014852000093</v>
       </c>
       <c r="F70">
-        <v>2.152826500172669</v>
+        <v>2.653808194772559</v>
       </c>
       <c r="G70">
-        <v>-4.60108672587699</v>
+        <v>-4.165028288535268</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.822298057841065</v>
       </c>
       <c r="E71">
-        <v>-16.42114093789983</v>
+        <v>-17.04081279263543</v>
       </c>
       <c r="F71">
-        <v>2.085283078883203</v>
+        <v>2.357050542924053</v>
       </c>
       <c r="G71">
-        <v>-5.473895504578142</v>
+        <v>-5.057071336819585</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.781727936043508</v>
       </c>
       <c r="E72">
-        <v>-16.65369166361572</v>
+        <v>-17.40602969288004</v>
       </c>
       <c r="F72">
-        <v>2.232908090470908</v>
+        <v>2.015244614976504</v>
       </c>
       <c r="G72">
-        <v>-4.40848911803881</v>
+        <v>-5.397041189883962</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.699590405985864</v>
       </c>
       <c r="E73">
-        <v>-16.51206363902584</v>
+        <v>-18.09051306761342</v>
       </c>
       <c r="F73">
-        <v>2.161867302006822</v>
+        <v>2.11276830930809</v>
       </c>
       <c r="G73">
-        <v>-4.820360709670617</v>
+        <v>-4.806211438035772</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.572921951029581</v>
       </c>
       <c r="E74">
-        <v>-16.87421476236725</v>
+        <v>-17.33016416782954</v>
       </c>
       <c r="F74">
-        <v>1.936968865616368</v>
+        <v>2.118812077878915</v>
       </c>
       <c r="G74">
-        <v>-3.845299110897996</v>
+        <v>-4.786215742978574</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.406817484540289</v>
       </c>
       <c r="E75">
-        <v>-17.32453527463801</v>
+        <v>-17.56114804153878</v>
       </c>
       <c r="F75">
-        <v>1.974049904035285</v>
+        <v>1.979417724805426</v>
       </c>
       <c r="G75">
-        <v>-4.246941116813455</v>
+        <v>-4.617162735015691</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.201581927739003</v>
       </c>
       <c r="E76">
-        <v>-16.431275662729</v>
+        <v>-17.78400330440425</v>
       </c>
       <c r="F76">
-        <v>1.941536483475404</v>
+        <v>2.345542862964362</v>
       </c>
       <c r="G76">
-        <v>-5.238770628742484</v>
+        <v>-3.727645632977837</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.960697819520258</v>
       </c>
       <c r="E77">
-        <v>-18.51468164248988</v>
+        <v>-18.3799051990736</v>
       </c>
       <c r="F77">
-        <v>2.052640433008485</v>
+        <v>1.79584985161025</v>
       </c>
       <c r="G77">
-        <v>-4.271041888339349</v>
+        <v>-4.022681451437685</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.695294531151282</v>
       </c>
       <c r="E78">
-        <v>-18.20758770613372</v>
+        <v>-18.40051881275651</v>
       </c>
       <c r="F78">
-        <v>1.514269547315836</v>
+        <v>1.904453788321682</v>
       </c>
       <c r="G78">
-        <v>-3.513658590410426</v>
+        <v>-4.327493310875001</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.409932650491523</v>
       </c>
       <c r="E79">
-        <v>-15.65576090349342</v>
+        <v>-18.76141102032379</v>
       </c>
       <c r="F79">
-        <v>1.43699115230867</v>
+        <v>1.724043651665977</v>
       </c>
       <c r="G79">
-        <v>-4.304375771374271</v>
+        <v>-3.645083937773953</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.109549120251972</v>
       </c>
       <c r="E80">
-        <v>-19.79805570473767</v>
+        <v>-19.51771146434482</v>
       </c>
       <c r="F80">
-        <v>1.45940843096323</v>
+        <v>1.67722763952936</v>
       </c>
       <c r="G80">
-        <v>-3.763859690631925</v>
+        <v>-4.535736556931777</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.805224544615937</v>
       </c>
       <c r="E81">
-        <v>-18.83788336089132</v>
+        <v>-20.5077762651158</v>
       </c>
       <c r="F81">
-        <v>1.565015334411334</v>
+        <v>1.593221244476657</v>
       </c>
       <c r="G81">
-        <v>-3.887488703250468</v>
+        <v>-3.582074324525005</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.501861011468529</v>
       </c>
       <c r="E82">
-        <v>-20.61657285315008</v>
+        <v>-19.71216866670819</v>
       </c>
       <c r="F82">
-        <v>1.692847335276548</v>
+        <v>1.593184796310934</v>
       </c>
       <c r="G82">
-        <v>-3.48974983052581</v>
+        <v>-3.439866530340071</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.204535251016122</v>
       </c>
       <c r="E83">
-        <v>-21.23811496765085</v>
+        <v>-22.46107918663632</v>
       </c>
       <c r="F83">
-        <v>1.129270886251516</v>
+        <v>1.522273233161685</v>
       </c>
       <c r="G83">
-        <v>-3.462159744001524</v>
+        <v>-2.888627592596026</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.924559666259851</v>
       </c>
       <c r="E84">
-        <v>-22.74975581920328</v>
+        <v>-22.34088895799874</v>
       </c>
       <c r="F84">
-        <v>1.592737477913422</v>
+        <v>1.218222634698932</v>
       </c>
       <c r="G84">
-        <v>-2.83051096565412</v>
+        <v>-2.364329874450569</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.666757454288001</v>
       </c>
       <c r="E85">
-        <v>-22.11267198190818</v>
+        <v>-23.44752120820116</v>
       </c>
       <c r="F85">
-        <v>0.9856965912634995</v>
+        <v>0.8849787122267189</v>
       </c>
       <c r="G85">
-        <v>-3.609273766675657</v>
+        <v>-3.183050960131109</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.43743567594495</v>
       </c>
       <c r="E86">
-        <v>-23.17452215264875</v>
+        <v>-25.1633283103894</v>
       </c>
       <c r="F86">
-        <v>0.8914333510293326</v>
+        <v>0.8840592244096114</v>
       </c>
       <c r="G86">
-        <v>-2.557129425566645</v>
+        <v>-3.122325623304258</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.247518111751342</v>
       </c>
       <c r="E87">
-        <v>-25.96758076567765</v>
+        <v>-24.85993866577152</v>
       </c>
       <c r="F87">
-        <v>0.5142420527363973</v>
+        <v>0.9980541761784626</v>
       </c>
       <c r="G87">
-        <v>-2.79494577492573</v>
+        <v>-2.821913478888633</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.101299197254401</v>
       </c>
       <c r="E88">
-        <v>-26.40187047996125</v>
+        <v>-27.34844834483657</v>
       </c>
       <c r="F88">
-        <v>0.3442055610659512</v>
+        <v>1.066189051793528</v>
       </c>
       <c r="G88">
-        <v>-3.105676889787263</v>
+        <v>-1.596005223514355</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.006457179887664</v>
       </c>
       <c r="E89">
-        <v>-28.30157438312698</v>
+        <v>-27.70307314437724</v>
       </c>
       <c r="F89">
-        <v>0.6771910329084909</v>
+        <v>0.5832202063675122</v>
       </c>
       <c r="G89">
-        <v>-2.573119360521325</v>
+        <v>-1.921342465295153</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.97333995777272</v>
       </c>
       <c r="E90">
-        <v>-29.43874892627413</v>
+        <v>-29.35070859885401</v>
       </c>
       <c r="F90">
-        <v>0.3732050471031563</v>
+        <v>0.4993504919362706</v>
       </c>
       <c r="G90">
-        <v>-2.318074932175873</v>
+        <v>-1.440260608619342</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.004070639059043</v>
       </c>
       <c r="E91">
-        <v>-29.04704271732166</v>
+        <v>-29.98075065906718</v>
       </c>
       <c r="F91">
-        <v>0.3859859277609499</v>
+        <v>0.1365205993056704</v>
       </c>
       <c r="G91">
-        <v>-1.921153764199414</v>
+        <v>-2.352822418156063</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.106047035610711</v>
       </c>
       <c r="E92">
-        <v>-31.6352014669255</v>
+        <v>-31.73585585869399</v>
       </c>
       <c r="F92">
-        <v>0.05842709077414978</v>
+        <v>-0.2755714744020137</v>
       </c>
       <c r="G92">
-        <v>-2.04309108804739</v>
+        <v>-2.935994878171918</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.2858764213881</v>
       </c>
       <c r="E93">
-        <v>-32.8852867167429</v>
+        <v>-33.66294797265811</v>
       </c>
       <c r="F93">
-        <v>-0.1958759033134788</v>
+        <v>-0.2886074922198695</v>
       </c>
       <c r="G93">
-        <v>-1.527447135941588</v>
+        <v>-2.786484020527353</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.539628885692066</v>
       </c>
       <c r="E94">
-        <v>-35.84440900010708</v>
+        <v>-35.4101306070085</v>
       </c>
       <c r="F94">
-        <v>-0.8132274790260468</v>
+        <v>-0.6037598706149414</v>
       </c>
       <c r="G94">
-        <v>-2.682145556766143</v>
+        <v>-2.276792429301161</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.867326037332715</v>
       </c>
       <c r="E95">
-        <v>-36.94469912246176</v>
+        <v>-37.8819596520663</v>
       </c>
       <c r="F95">
-        <v>-0.8471317284552278</v>
+        <v>-0.8948158696299785</v>
       </c>
       <c r="G95">
-        <v>-2.451397222133402</v>
+        <v>-3.478550254966455</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.269194103058525</v>
       </c>
       <c r="E96">
-        <v>-40.0164445543967</v>
+        <v>-38.72707252832576</v>
       </c>
       <c r="F96">
-        <v>-0.9496637321041393</v>
+        <v>-1.54042968439126</v>
       </c>
       <c r="G96">
-        <v>-2.533409366777767</v>
+        <v>-2.13148596449147</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.725635346943828</v>
       </c>
       <c r="E97">
-        <v>-41.87672129861465</v>
+        <v>-41.4348441261312</v>
       </c>
       <c r="F97">
-        <v>-1.087398865269822</v>
+        <v>-1.742700436806843</v>
       </c>
       <c r="G97">
-        <v>-3.395683989572958</v>
+        <v>-2.828971561978359</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.235216223109134</v>
       </c>
       <c r="E98">
-        <v>-43.64086080388676</v>
+        <v>-42.78335349426831</v>
       </c>
       <c r="F98">
-        <v>-1.982289140718544</v>
+        <v>-1.74340372073182</v>
       </c>
       <c r="G98">
-        <v>-3.318617799964264</v>
+        <v>-3.224979019385978</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.767220461277065</v>
       </c>
       <c r="E99">
-        <v>-45.52649020983665</v>
+        <v>-45.09470474167929</v>
       </c>
       <c r="F99">
-        <v>-2.021543815202407</v>
+        <v>-1.970610817073877</v>
       </c>
       <c r="G99">
-        <v>-3.382127305589643</v>
+        <v>-3.34761817888828</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.321519685550829</v>
       </c>
       <c r="E100">
-        <v>-48.36572793655877</v>
+        <v>-47.32452534305617</v>
       </c>
       <c r="F100">
-        <v>-2.161639795466068</v>
+        <v>-2.558171815879566</v>
       </c>
       <c r="G100">
-        <v>-5.073024855773333</v>
+        <v>-2.969285724114829</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.838594739482742</v>
       </c>
       <c r="E101">
-        <v>-48.46468188633738</v>
+        <v>-49.67574867198619</v>
       </c>
       <c r="F101">
-        <v>-2.393056654949152</v>
+        <v>-2.36470909405795</v>
       </c>
       <c r="G101">
-        <v>-3.587659214849755</v>
+        <v>-3.838767404549014</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.362267129057155</v>
       </c>
       <c r="E102">
-        <v>-50.70280997328133</v>
+        <v>-51.20421846506962</v>
       </c>
       <c r="F102">
-        <v>-2.992973581934999</v>
+        <v>-2.740917120243762</v>
       </c>
       <c r="G102">
-        <v>-4.052665062386865</v>
+        <v>-4.947667738383291</v>
       </c>
     </row>
   </sheetData>
